--- a/templates/detmir_links_template.xlsx
+++ b/templates/detmir_links_template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ссылки Детский Мир" sheetId="1" r:id="R07a38cf0b2c646af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как собрать файл" sheetId="2" r:id="Rb58cad7962f249f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ссылки Детский Мир" sheetId="1" r:id="Rf46713a48e1f4648"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как собрать файл" sheetId="2" r:id="Rb8c61b9df21c4521"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -289,129 +289,102 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30.709999084472656" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="99.29000091552734" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30.709999084472656" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="107.86000061035156" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="12" t="str">
-        <x:v>article</x:v>
+        <x:v>Штрихкод товара</x:v>
       </x:c>
       <x:c r="B1" s="12" t="str">
-        <x:v>Штрихкод товара</x:v>
-      </x:c>
-      <x:c r="C1" s="12" t="str">
         <x:v>Ссылки на фото</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="13" t="str">
-        <x:v>TSR-10025</x:v>
+        <x:v>4607000012345</x:v>
       </x:c>
       <x:c r="B2" s="13" t="str">
-        <x:v>4607000012345</x:v>
-      </x:c>
-      <x:c r="C2" s="13" t="str">
         <x:v>https://static.detmir.st/media_out/523/698/3698523/1500/0.jpg
 https://static.detmir.st/media_out/523/698/3698523/1500/1.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="13" t="str">
-        <x:v>TSR-10026</x:v>
+        <x:v>4607000012346</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>4607000012346</x:v>
-      </x:c>
-      <x:c r="C3" s="13" t="str">
         <x:v>https://disk.yandex.ru/d/example-public-link</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str"/>
       <x:c r="B4" s="14" t="str"/>
-      <x:c r="C4" s="14" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14"/>
       <x:c r="B5" s="14"/>
-      <x:c r="C5" s="14"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14"/>
       <x:c r="B6" s="14"/>
-      <x:c r="C6" s="14"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14"/>
       <x:c r="B7" s="14"/>
-      <x:c r="C7" s="14"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14"/>
       <x:c r="B8" s="14"/>
-      <x:c r="C8" s="14"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14"/>
       <x:c r="B9" s="14"/>
-      <x:c r="C9" s="14"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14"/>
       <x:c r="B10" s="14"/>
-      <x:c r="C10" s="14"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14"/>
       <x:c r="B11" s="14"/>
-      <x:c r="C11" s="14"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14"/>
       <x:c r="B12" s="14"/>
-      <x:c r="C12" s="14"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14"/>
       <x:c r="B13" s="14"/>
-      <x:c r="C13" s="14"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14"/>
       <x:c r="B14" s="14"/>
-      <x:c r="C14" s="14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14"/>
       <x:c r="B15" s="14"/>
-      <x:c r="C15" s="14"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="14"/>
       <x:c r="B16" s="14"/>
-      <x:c r="C16" s="14"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="14"/>
       <x:c r="B17" s="14"/>
-      <x:c r="C17" s="14"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="14"/>
       <x:c r="B18" s="14"/>
-      <x:c r="C18" s="14"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="14"/>
       <x:c r="B19" s="14"/>
-      <x:c r="C19" s="14"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="14"/>
       <x:c r="B20" s="14"/>
-      <x:c r="C20" s="14"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -491,7 +464,7 @@
         <x:v>Загрузить файл в блок Готовые ссылки без парсинга</x:v>
       </x:c>
       <x:c r="C7" s="28" t="str">
-        <x:v>Сервис соберёт итоговый Excel</x:v>
+        <x:v>Сервис соберёт итоговый Excel под Детский Мир</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
